--- a/Dualismo_Particella-Onda.xlsx
+++ b/Dualismo_Particella-Onda.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carmelo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\Esperienza_Laboratorio_DOP\Analisi_Dati_DOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B2DD43B-8363-8A40-99CB-AE8B5BF3DB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4E6AB7-FE17-4A60-A8BE-7B63EF510482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{506A3D08-F08A-1E43-B450-3F1A0734760D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{506A3D08-F08A-1E43-B450-3F1A0734760D}"/>
   </bookViews>
   <sheets>
     <sheet name="1°parte" sheetId="1" r:id="rId1"/>
-    <sheet name="2°parte" sheetId="2" r:id="rId2"/>
-    <sheet name="2° PARTE" sheetId="3" r:id="rId3"/>
+    <sheet name="OBSOLETO_2°parte" sheetId="2" r:id="rId2"/>
+    <sheet name="OBSOLETO_2° PARTE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -400,7 +400,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000000E+00"/>
-    <numFmt numFmtId="169" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="168" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -829,7 +829,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -917,6 +917,64 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -929,12 +987,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -944,67 +996,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1460,10 +1457,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
@@ -1782,49 +1775,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{775B02F6-2E8D-E24B-BDC8-854D4CF7062C}">
   <dimension ref="A1:U50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="34.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.296875" customWidth="1"/>
+    <col min="3" max="3" width="34.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.296875" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.296875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16" customHeight="1">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:21" ht="16.05" customHeight="1">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65" t="s">
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="N1" s="64" t="s">
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="N1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
       <c r="U1" t="s">
         <v>2</v>
       </c>
@@ -2244,34 +2237,34 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:21" ht="16" customHeight="1">
-      <c r="A12" s="66" t="s">
+    <row r="12" spans="1:21" ht="16.05" customHeight="1">
+      <c r="A12" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66" t="s">
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="63" t="s">
+      <c r="N12" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="O12" s="64"/>
-      <c r="P12" s="64"/>
-      <c r="Q12" s="64"/>
-      <c r="R12" s="64"/>
-      <c r="S12" s="64"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="16" t="s">
@@ -3069,90 +3062,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46950218-72AB-47A9-80E6-BD5966BA40BB}">
   <dimension ref="A1:AN40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="11.296875" customWidth="1"/>
+    <col min="4" max="4" width="13.796875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="13.796875" customWidth="1"/>
+    <col min="9" max="9" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.296875" customWidth="1"/>
     <col min="30" max="30" width="13.5" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.296875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.296875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.296875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="I1" s="68" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="I1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
       <c r="U1" s="57" t="s">
         <v>22</v>
       </c>
       <c r="V1" s="57"/>
       <c r="W1" s="57"/>
       <c r="X1" s="57"/>
-      <c r="Z1" s="68" t="s">
+      <c r="Z1" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="68"/>
-      <c r="AF1" s="68"/>
-      <c r="AG1" s="68"/>
-      <c r="AI1" s="67" t="s">
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="97"/>
+      <c r="AD1" s="97"/>
+      <c r="AE1" s="97"/>
+      <c r="AF1" s="97"/>
+      <c r="AG1" s="97"/>
+      <c r="AI1" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="AJ1" s="67"/>
-      <c r="AK1" s="67"/>
-      <c r="AL1" s="67"/>
-      <c r="AM1" s="67"/>
-      <c r="AN1" s="67"/>
+      <c r="AJ1" s="96"/>
+      <c r="AK1" s="96"/>
+      <c r="AL1" s="96"/>
+      <c r="AM1" s="96"/>
+      <c r="AN1" s="96"/>
     </row>
     <row r="2" spans="1:40">
       <c r="A2" s="22" t="s">
@@ -3224,18 +3217,18 @@
       <c r="AG2" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="AI2" s="67" t="s">
+      <c r="AI2" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="AJ2" s="67"/>
-      <c r="AK2" s="67">
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="96">
         <v>10</v>
       </c>
-      <c r="AL2" s="67"/>
-      <c r="AM2" s="67">
+      <c r="AL2" s="96"/>
+      <c r="AM2" s="96">
         <v>11</v>
       </c>
-      <c r="AN2" s="67"/>
+      <c r="AN2" s="96"/>
     </row>
     <row r="3" spans="1:40">
       <c r="A3" s="53">
@@ -3402,7 +3395,7 @@
         <f t="shared" ref="AG4:AG7" si="7">($E$3*AD4)/$F$3</f>
         <v>2.4654612E-11</v>
       </c>
-      <c r="AI4" s="73">
+      <c r="AI4" s="63">
         <f>Z11*10^9</f>
         <v>2.1033032607676899E-2</v>
       </c>
@@ -3486,7 +3479,7 @@
         <f t="shared" si="7"/>
         <v>2.3605176E-11</v>
       </c>
-      <c r="AI5" s="73">
+      <c r="AI5" s="63">
         <f t="shared" ref="AI5:AI8" si="8">Z12*10^9</f>
         <v>1.9895257080236345E-2</v>
       </c>
@@ -3573,7 +3566,7 @@
         <f t="shared" si="7"/>
         <v>2.3627316000000002E-11</v>
       </c>
-      <c r="AI6" s="73">
+      <c r="AI6" s="63">
         <f t="shared" si="8"/>
         <v>1.9153556418772019E-2</v>
       </c>
@@ -3599,22 +3592,22 @@
       </c>
     </row>
     <row r="7" spans="1:40">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="74" t="s">
+      <c r="E7" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="64" t="s">
         <v>92</v>
       </c>
       <c r="I7" s="55">
@@ -3675,7 +3668,7 @@
         <f t="shared" si="7"/>
         <v>2.2599036000000004E-11</v>
       </c>
-      <c r="AI7" s="73">
+      <c r="AI7" s="63">
         <f t="shared" si="8"/>
         <v>1.8595023226764654E-2</v>
       </c>
@@ -3701,22 +3694,22 @@
       </c>
     </row>
     <row r="8" spans="1:40">
-      <c r="A8" s="75">
+      <c r="A8" s="65">
         <v>2900</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="65">
         <v>14.132897524374499</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="65">
         <v>1.6132140106919</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="65">
         <v>24.5109397376423</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="65">
         <v>1.82238327806422</v>
       </c>
       <c r="I8" s="55">
@@ -3753,7 +3746,7 @@
       <c r="AC8" s="60"/>
       <c r="AD8" s="60"/>
       <c r="AE8" s="60"/>
-      <c r="AI8" s="73">
+      <c r="AI8" s="63">
         <f t="shared" si="8"/>
         <v>1.8282479568623063E-2</v>
       </c>
@@ -3779,22 +3772,22 @@
       </c>
     </row>
     <row r="9" spans="1:40">
-      <c r="A9" s="75">
+      <c r="A9" s="65">
         <v>3200</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="65">
         <v>15.7321625477409</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="65">
         <v>1.62097280861413</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="65">
         <v>27.627634215834401</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="65">
         <v>1.67735020829843</v>
       </c>
       <c r="U9" s="58">
@@ -3802,22 +3795,22 @@
       </c>
     </row>
     <row r="10" spans="1:40">
-      <c r="A10" s="75">
+      <c r="A10" s="65">
         <v>3300</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="65">
         <v>15.625893748029901</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="65">
         <v>1.6937381733540999</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="65">
         <v>24.358215545555002</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="65">
         <v>4.6691997856601297</v>
       </c>
       <c r="I10" s="51" t="s">
@@ -3864,22 +3857,22 @@
       </c>
     </row>
     <row r="11" spans="1:40">
-      <c r="A11" s="75">
+      <c r="A11" s="65">
         <v>3400</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="65">
         <v>15.421207002041299</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="65">
         <v>0.75790923401883004</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="65">
         <v>27.434546940849302</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="65">
         <v>1.0732065597335601</v>
       </c>
       <c r="I11" s="50">
@@ -3941,26 +3934,26 @@
       </c>
     </row>
     <row r="12" spans="1:40">
-      <c r="A12" s="75">
+      <c r="A12" s="65">
         <v>3600</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="65">
         <v>14.276839465305001</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="65">
         <v>1.5944380727905101</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="65">
         <v>24.570261486439801</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="65">
         <v>1.7789713970628001</v>
       </c>
       <c r="I12" s="50">
-        <f t="shared" ref="I11:I16" si="16">($A$3)/(SQRT(2*$C$3*$B$3*I4*10^3))</f>
+        <f t="shared" ref="I12:I16" si="16">($A$3)/(SQRT(2*$C$3*$B$3*I4*10^3))</f>
         <v>2.0440433556346103E-11</v>
       </c>
       <c r="J12" s="50">
@@ -4018,22 +4011,22 @@
       </c>
     </row>
     <row r="13" spans="1:40">
-      <c r="A13" s="75">
+      <c r="A13" s="65">
         <v>3600</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="65">
         <v>14.608209450585599</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="65">
         <v>1.65422061844574</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="65">
         <v>25.280442414886799</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="65">
         <v>1.7722852073505899</v>
       </c>
       <c r="I13" s="50">
@@ -4095,22 +4088,22 @@
       </c>
     </row>
     <row r="14" spans="1:40">
-      <c r="A14" s="75">
+      <c r="A14" s="65">
         <v>3750</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="65">
         <v>14.752239984701299</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="65">
         <v>1.5544896639771899</v>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="65">
         <v>25.5865516555229</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="65">
         <v>1.6557699404670601</v>
       </c>
       <c r="I14" s="50">
@@ -4172,22 +4165,22 @@
       </c>
     </row>
     <row r="15" spans="1:40">
-      <c r="A15" s="75">
+      <c r="A15" s="65">
         <v>3800</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="65">
         <v>14.837621682306599</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="65">
         <v>0.87554886606265003</v>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="65">
         <v>25.0516734432418</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="65">
         <v>1.08795415484975</v>
       </c>
       <c r="I15" s="50">
@@ -4249,22 +4242,22 @@
       </c>
     </row>
     <row r="16" spans="1:40">
-      <c r="A16" s="75">
+      <c r="A16" s="65">
         <v>3900</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="65">
         <v>13.8932319612138</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="65">
         <v>1.5845935583510899</v>
       </c>
-      <c r="E16" s="75">
+      <c r="E16" s="65">
         <v>23.5846443194594</v>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="65">
         <v>1.7056280294042601</v>
       </c>
       <c r="I16" s="50">
@@ -4288,22 +4281,22 @@
       <c r="AG16" s="1"/>
     </row>
     <row r="17" spans="1:36">
-      <c r="A17" s="75">
+      <c r="A17" s="65">
         <v>4000</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="75">
+      <c r="C17" s="65">
         <v>14.159840771141599</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="65">
         <v>1.41688638932538</v>
       </c>
-      <c r="E17" s="75">
+      <c r="E17" s="65">
         <v>24.307674223869199</v>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="65">
         <v>1.67317466996315</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -4324,37 +4317,37 @@
       <c r="O17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Z17" s="69" t="s">
+      <c r="Z17" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
-      <c r="AC17" s="70"/>
-      <c r="AD17" s="70"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="71"/>
+      <c r="AA17" s="94"/>
+      <c r="AB17" s="94"/>
+      <c r="AC17" s="94"/>
+      <c r="AD17" s="94"/>
+      <c r="AE17" s="94"/>
+      <c r="AF17" s="94"/>
+      <c r="AG17" s="94"/>
+      <c r="AH17" s="95"/>
       <c r="AI17" s="61"/>
       <c r="AJ17" s="62"/>
     </row>
     <row r="18" spans="1:36">
-      <c r="A18" s="75">
+      <c r="A18" s="65">
         <v>4050</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="75">
+      <c r="C18" s="65">
         <v>14.202986215545801</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="65">
         <v>1.5927004496706401</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="65">
         <v>24.109663560267101</v>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="65">
         <v>1.7477286396192699</v>
       </c>
       <c r="I18" s="1">
@@ -4395,26 +4388,26 @@
       </c>
     </row>
     <row r="19" spans="1:36">
-      <c r="A19" s="75">
+      <c r="A19" s="65">
         <v>4100</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="75">
+      <c r="C19" s="65">
         <v>14.1477581631242</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="65">
         <v>0.96726917441917404</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="65">
         <v>23.991469043145798</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="65">
         <v>1.0661672525943</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" ref="I18:I23" si="29">($D$3*K4)/$F$3</f>
+        <f t="shared" ref="I19:I23" si="29">($D$3*K4)/$F$3</f>
         <v>2.6058846000000008E-11</v>
       </c>
       <c r="J19" s="50">
@@ -4448,22 +4441,22 @@
       </c>
     </row>
     <row r="20" spans="1:36">
-      <c r="A20" s="75">
+      <c r="A20" s="65">
         <v>4200</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="65">
         <v>13.998592400678501</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="65">
         <v>1.4551827892046001</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="65">
         <v>23.585214490292302</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="65">
         <v>1.5773710744623799</v>
       </c>
       <c r="I20" s="1">
@@ -4501,22 +4494,22 @@
       </c>
     </row>
     <row r="21" spans="1:36">
-      <c r="A21" s="75">
+      <c r="A21" s="65">
         <v>4350</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="75">
+      <c r="C21" s="65">
         <v>12.7285216590373</v>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="65">
         <v>1.5238300246508001</v>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="65">
         <v>21.3442985608926</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="65">
         <v>1.6759499431585601</v>
       </c>
       <c r="I21" s="1">
@@ -4554,22 +4547,22 @@
       </c>
     </row>
     <row r="22" spans="1:36">
-      <c r="A22" s="75">
+      <c r="A22" s="65">
         <v>4350</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="65">
         <v>14.295788703025901</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="65">
         <v>0.95743396407127301</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="65">
         <v>24.0058440474461</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="65">
         <v>1.0609821789779801</v>
       </c>
       <c r="I22" s="1">
@@ -4607,22 +4600,22 @@
       </c>
     </row>
     <row r="23" spans="1:36">
-      <c r="A23" s="75">
+      <c r="A23" s="65">
         <v>4500</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="75">
+      <c r="C23" s="65">
         <v>12.652912148520899</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="65">
         <v>1.2770471819939999</v>
       </c>
-      <c r="E23" s="75">
+      <c r="E23" s="65">
         <v>21.557679219558601</v>
       </c>
-      <c r="F23" s="75">
+      <c r="F23" s="65">
         <v>1.4151791181836999</v>
       </c>
       <c r="I23" s="1">
@@ -4660,53 +4653,53 @@
       </c>
     </row>
     <row r="24" spans="1:36">
-      <c r="A24" s="75">
+      <c r="A24" s="65">
         <v>4500</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="75">
+      <c r="C24" s="65">
         <v>13.8576230407855</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="65">
         <v>0.96053842000012601</v>
       </c>
-      <c r="E24" s="75">
+      <c r="E24" s="65">
         <v>22.9614197110436</v>
       </c>
-      <c r="F24" s="75">
+      <c r="F24" s="65">
         <v>1.05034657780143</v>
       </c>
-      <c r="I24" s="69" t="s">
+      <c r="I24" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="70"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="71"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="95"/>
     </row>
     <row r="25" spans="1:36">
-      <c r="A25" s="75">
+      <c r="A25" s="65">
         <v>4550</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="75">
+      <c r="C25" s="65">
         <v>11.9846211346032</v>
       </c>
-      <c r="D25" s="75">
+      <c r="D25" s="65">
         <v>1.90488620765271</v>
       </c>
-      <c r="E25" s="75">
+      <c r="E25" s="65">
         <v>20.0178224383173</v>
       </c>
-      <c r="F25" s="75">
+      <c r="F25" s="65">
         <v>1.5035019813438499</v>
       </c>
       <c r="I25" s="22" t="s">
@@ -4911,107 +4904,107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B129EF39-A454-004A-A23E-E3E882CD1EF9}">
-  <dimension ref="A1:BU28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:BT28"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14" customWidth="1"/>
     <col min="33" max="33" width="11" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="I1" s="85" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="I1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="O1" s="82" t="s">
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="O1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="U1" s="81" t="s">
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="U1" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="AB1" s="93" t="s">
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="AB1" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="AC1" s="93"/>
-      <c r="AD1" s="93"/>
-      <c r="AE1" s="93"/>
-      <c r="AF1" s="93"/>
-      <c r="AG1" s="93"/>
-      <c r="AH1" s="93"/>
-      <c r="AI1" s="93"/>
-      <c r="AJ1" s="93"/>
-      <c r="AK1" s="93"/>
-      <c r="AL1" s="93"/>
-      <c r="AM1" s="93"/>
-      <c r="AN1" s="93"/>
-      <c r="AR1" s="92" t="s">
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="82"/>
+      <c r="AJ1" s="82"/>
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="82"/>
+      <c r="AM1" s="82"/>
+      <c r="AN1" s="82"/>
+      <c r="AR1" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="AS1" s="92"/>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
-      <c r="BB1" s="92"/>
-      <c r="BC1" s="92"/>
-      <c r="BD1" s="92"/>
-      <c r="BH1" s="94" t="s">
+      <c r="AS1" s="83"/>
+      <c r="AT1" s="83"/>
+      <c r="AU1" s="83"/>
+      <c r="AV1" s="83"/>
+      <c r="AW1" s="83"/>
+      <c r="AX1" s="83"/>
+      <c r="AY1" s="83"/>
+      <c r="AZ1" s="83"/>
+      <c r="BA1" s="83"/>
+      <c r="BB1" s="83"/>
+      <c r="BC1" s="83"/>
+      <c r="BD1" s="83"/>
+      <c r="BH1" s="84" t="s">
         <v>109</v>
       </c>
-      <c r="BI1" s="94"/>
-      <c r="BJ1" s="94"/>
-      <c r="BK1" s="94"/>
-      <c r="BL1" s="94"/>
-      <c r="BM1" s="94"/>
-      <c r="BN1" s="94"/>
-      <c r="BO1" s="94"/>
-      <c r="BP1" s="94"/>
-      <c r="BQ1" s="94"/>
-      <c r="BR1" s="94"/>
-      <c r="BS1" s="94"/>
-      <c r="BT1" s="94"/>
+      <c r="BI1" s="84"/>
+      <c r="BJ1" s="84"/>
+      <c r="BK1" s="84"/>
+      <c r="BL1" s="84"/>
+      <c r="BM1" s="84"/>
+      <c r="BN1" s="84"/>
+      <c r="BO1" s="84"/>
+      <c r="BP1" s="84"/>
+      <c r="BQ1" s="84"/>
+      <c r="BR1" s="84"/>
+      <c r="BS1" s="84"/>
+      <c r="BT1" s="84"/>
     </row>
     <row r="2" spans="1:72">
       <c r="A2" s="22" t="s">
@@ -5071,16 +5064,16 @@
       <c r="X2" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="AB2" s="89" t="s">
+      <c r="AB2" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="AC2" s="89" t="s">
+      <c r="AC2" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="AD2" s="90" t="s">
+      <c r="AD2" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="AE2" s="90" t="s">
+      <c r="AE2" s="75" t="s">
         <v>98</v>
       </c>
       <c r="AG2" s="22" t="s">
@@ -5107,16 +5100,16 @@
       <c r="AN2" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="AR2" s="89" t="s">
+      <c r="AR2" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="AS2" s="89" t="s">
+      <c r="AS2" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="AT2" s="90" t="s">
+      <c r="AT2" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="AU2" s="90" t="s">
+      <c r="AU2" s="75" t="s">
         <v>98</v>
       </c>
       <c r="AW2" s="22" t="s">
@@ -5143,16 +5136,16 @@
       <c r="BD2" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="BH2" s="96" t="s">
+      <c r="BH2" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="BI2" s="96" t="s">
+      <c r="BI2" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="BJ2" s="97" t="s">
+      <c r="BJ2" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="BK2" s="97" t="s">
+      <c r="BK2" s="77" t="s">
         <v>98</v>
       </c>
       <c r="BM2" s="22" t="s">
@@ -5247,7 +5240,7 @@
         <f>C13*10^-3</f>
         <v>1.54212070020413E-2</v>
       </c>
-      <c r="X3" s="86">
+      <c r="X3" s="71">
         <f>E13*10^-3</f>
         <v>2.7434546940849302E-2</v>
       </c>
@@ -5300,19 +5293,19 @@
         <v>4.6104697307382154E-3</v>
       </c>
       <c r="AR3" s="56">
-        <f>C10*10^-3</f>
+        <f t="shared" ref="AR3:AU4" si="0">C10*10^-3</f>
         <v>1.4132897524374499E-2</v>
       </c>
       <c r="AS3" s="56">
-        <f>D10*10^-3</f>
+        <f t="shared" si="0"/>
         <v>1.6132140106919E-3</v>
       </c>
       <c r="AT3" s="56">
-        <f>E10*10^-3</f>
+        <f t="shared" si="0"/>
         <v>2.45109397376423E-2</v>
       </c>
       <c r="AU3" s="56">
-        <f>F10*10^-3</f>
+        <f t="shared" si="0"/>
         <v>1.82238327806422E-3</v>
       </c>
       <c r="AW3" s="55">
@@ -5355,11 +5348,11 @@
         <f>D13*10^-3</f>
         <v>7.5790923401883E-4</v>
       </c>
-      <c r="BJ3" s="86">
+      <c r="BJ3" s="71">
         <f>E13*10^-3</f>
         <v>2.7434546940849302E-2</v>
       </c>
-      <c r="BK3" s="86">
+      <c r="BK3" s="71">
         <f>F13*10^-3</f>
         <v>1.07320655973356E-3</v>
       </c>
@@ -5435,7 +5428,7 @@
         <f>C17*10^-3</f>
         <v>1.4837621682306599E-2</v>
       </c>
-      <c r="X4" s="86">
+      <c r="X4" s="71">
         <f>E17*10^-3</f>
         <v>2.5051673443241801E-2</v>
       </c>
@@ -5456,83 +5449,83 @@
         <v>1.7789713970628E-3</v>
       </c>
       <c r="AG4" s="55">
-        <f t="shared" ref="AG4:AG7" si="0">I4</f>
+        <f t="shared" ref="AG4:AG7" si="1">I4</f>
         <v>3.6</v>
       </c>
       <c r="AH4" s="55">
-        <f t="shared" ref="AH4:AH8" si="1">J4</f>
+        <f t="shared" ref="AH4:AH8" si="2">J4</f>
         <v>0.05</v>
       </c>
       <c r="AI4" s="50">
-        <f t="shared" ref="AI4:AI7" si="2">AB13*10^9</f>
+        <f t="shared" ref="AI4:AI7" si="3">AB13*10^9</f>
         <v>2.0440433556346102E-2</v>
       </c>
       <c r="AJ4" s="50">
-        <f t="shared" ref="AJ4:AJ8" si="3">AD13*10^9</f>
+        <f t="shared" ref="AJ4:AJ8" si="4">AD13*10^9</f>
         <v>1.4194745525240374E-4</v>
       </c>
       <c r="AK4" s="50">
-        <f t="shared" ref="AK4:AK8" si="4">AF13*10^9</f>
+        <f t="shared" ref="AK4:AK8" si="5">AF13*10^9</f>
         <v>2.4327734448879725E-2</v>
       </c>
       <c r="AL4" s="50">
-        <f t="shared" ref="AL4:AL8" si="5">AI13*10^9</f>
+        <f t="shared" ref="AL4:AL8" si="6">AI13*10^9</f>
         <v>2.7169224760350296E-3</v>
       </c>
       <c r="AM4" s="22">
-        <f t="shared" ref="AM4:AM8" si="6">AK13*10^9</f>
+        <f t="shared" ref="AM4:AM6" si="7">AK13*10^9</f>
         <v>2.4177137302656769E-2</v>
       </c>
       <c r="AN4" s="22">
-        <f t="shared" ref="AN4:AN8" si="7">AN13*10^9</f>
+        <f t="shared" ref="AN4:AN8" si="8">AN13*10^9</f>
         <v>1.7505078547097954E-3</v>
       </c>
       <c r="AR4" s="56">
-        <f>C11*10^-3</f>
+        <f t="shared" si="0"/>
         <v>1.5732162547740902E-2</v>
       </c>
       <c r="AS4" s="56">
-        <f>D11*10^-3</f>
+        <f t="shared" si="0"/>
         <v>1.6209728086141299E-3</v>
       </c>
       <c r="AT4" s="56">
-        <f>E11*10^-3</f>
+        <f t="shared" si="0"/>
         <v>2.7627634215834401E-2</v>
       </c>
       <c r="AU4" s="56">
-        <f>F11*10^-3</f>
+        <f t="shared" si="0"/>
         <v>1.6773502082984299E-3</v>
       </c>
       <c r="AW4" s="55">
-        <f t="shared" ref="AW4:AW7" si="8">O4</f>
+        <f t="shared" ref="AW4:AW7" si="9">O4</f>
         <v>3.2</v>
       </c>
       <c r="AX4" s="55">
-        <f t="shared" ref="AX4:AX9" si="9">P4</f>
+        <f t="shared" ref="AX4:AX9" si="10">P4</f>
         <v>0.05</v>
       </c>
       <c r="AY4" s="50">
-        <f t="shared" ref="AY4:AY9" si="10">AR13*10^9</f>
+        <f t="shared" ref="AY4:AY9" si="11">AR13*10^9</f>
         <v>2.1680353767128076E-2</v>
       </c>
       <c r="AZ4" s="50">
-        <f t="shared" ref="AZ4:AZ9" si="11">AT13*10^9</f>
+        <f t="shared" ref="AZ4:AZ8" si="12">AT13*10^9</f>
         <v>1.6937776380568788E-4</v>
       </c>
       <c r="BA4" s="50">
-        <f t="shared" ref="BA4:BA9" si="12">AV13*10^9</f>
+        <f t="shared" ref="BA4:BA9" si="13">AV13*10^9</f>
         <v>2.68076049813505E-2</v>
       </c>
       <c r="BB4" s="50">
-        <f t="shared" ref="BB4:BB9" si="13">AY13*10^9</f>
+        <f t="shared" ref="BB4:BB9" si="14">AY13*10^9</f>
         <v>4.2136793498428471E-3</v>
       </c>
       <c r="BC4" s="22">
-        <f t="shared" ref="BC4:BC9" si="14">BA13*10^9</f>
+        <f t="shared" ref="BC4:BC9" si="15">BA13*10^9</f>
         <v>2.7185592068381052E-2</v>
       </c>
       <c r="BD4" s="22">
-        <f t="shared" ref="BD4:BD9" si="15">BD13*10^9</f>
+        <f t="shared" ref="BD4:BD9" si="16">BD13*10^9</f>
         <v>3.6245604492897297E-3</v>
       </c>
       <c r="BH4" s="56">
@@ -5543,44 +5536,44 @@
         <f>D17*10^-3</f>
         <v>8.7554886606265006E-4</v>
       </c>
-      <c r="BJ4" s="86">
+      <c r="BJ4" s="71">
         <f>E17*10^-3</f>
         <v>2.5051673443241801E-2</v>
       </c>
-      <c r="BK4" s="86">
+      <c r="BK4" s="71">
         <f>F17*10^-3</f>
         <v>1.0879541548497501E-3</v>
       </c>
       <c r="BM4" s="55">
-        <f t="shared" ref="BM4:BM7" si="16">U4</f>
+        <f t="shared" ref="BM4:BM7" si="17">U4</f>
         <v>3.8</v>
       </c>
       <c r="BN4" s="55">
-        <f t="shared" ref="BN4:BN7" si="17">V4</f>
+        <f t="shared" ref="BN4:BN7" si="18">V4</f>
         <v>0.05</v>
       </c>
       <c r="BO4" s="50">
-        <f t="shared" ref="BO4:BO7" si="18">BH13*10^9</f>
+        <f t="shared" ref="BO4:BO7" si="19">BH13*10^9</f>
         <v>1.9895257080236345E-2</v>
       </c>
       <c r="BP4" s="50">
-        <f t="shared" ref="BP4:BP7" si="19">BJ13*10^9</f>
+        <f t="shared" ref="BP4:BP7" si="20">BJ13*10^9</f>
         <v>1.3088984921208103E-4</v>
       </c>
       <c r="BQ4" s="50">
-        <f t="shared" ref="BQ4:BQ7" si="20">BL13*10^9</f>
+        <f t="shared" ref="BQ4:BQ7" si="21">BL13*10^9</f>
         <v>2.5283307346650446E-2</v>
       </c>
       <c r="BR4" s="50">
-        <f t="shared" ref="BR4:BR7" si="21">BO13*10^9</f>
+        <f t="shared" ref="BR4:BR7" si="22">BO13*10^9</f>
         <v>5.1127449652982717E-3</v>
       </c>
       <c r="BS4" s="22">
-        <f t="shared" ref="BS4:BS7" si="22">BQ13*10^9</f>
+        <f t="shared" ref="BS4:BS7" si="23">BQ13*10^9</f>
         <v>2.4650846668149935E-2</v>
       </c>
       <c r="BT4" s="22">
-        <f t="shared" ref="BT4:BT7" si="23">BT13*10^9</f>
+        <f t="shared" ref="BT4:BT7" si="24">BT13*10^9</f>
         <v>4.8866036900283693E-3</v>
       </c>
     </row>
@@ -5623,7 +5616,7 @@
         <f>C21*10^-3</f>
         <v>1.41477581631242E-2</v>
       </c>
-      <c r="X5" s="86">
+      <c r="X5" s="71">
         <f>E21*10^-3</f>
         <v>2.3991469043145797E-2</v>
       </c>
@@ -5644,83 +5637,83 @@
         <v>1.7056280294042601E-3</v>
       </c>
       <c r="AG5" s="55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9</v>
       </c>
       <c r="AH5" s="55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
       <c r="AI5" s="50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.9638533330119515E-2</v>
       </c>
       <c r="AJ5" s="50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2588803416743291E-4</v>
       </c>
       <c r="AK5" s="50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.3674067261908315E-2</v>
       </c>
       <c r="AL5" s="50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.7001474234302578E-3</v>
       </c>
       <c r="AM5" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.3207290010348054E-2</v>
       </c>
       <c r="AN5" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.6783379809337921E-3</v>
       </c>
       <c r="AR5" s="56">
-        <f>C15*10^-3</f>
+        <f t="shared" ref="AR5:AU6" si="25">C15*10^-3</f>
         <v>1.4608209450585601E-2</v>
       </c>
       <c r="AS5" s="56">
-        <f>D15*10^-3</f>
+        <f t="shared" si="25"/>
         <v>1.65422061844574E-3</v>
       </c>
       <c r="AT5" s="56">
-        <f>E15*10^-3</f>
+        <f t="shared" si="25"/>
         <v>2.5280442414886799E-2</v>
       </c>
       <c r="AU5" s="56">
-        <f>F15*10^-3</f>
+        <f t="shared" si="25"/>
         <v>1.77228520735059E-3</v>
       </c>
       <c r="AW5" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AX5" s="55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
       <c r="AY5" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0440433556346102E-2</v>
       </c>
       <c r="AZ5" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4194745525240374E-4</v>
       </c>
       <c r="BA5" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4892388903797864E-2</v>
       </c>
       <c r="BB5" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.985369854428553E-3</v>
       </c>
       <c r="BC5" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.487595533624861E-2</v>
       </c>
       <c r="BD5" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.3118567217586101E-3</v>
       </c>
       <c r="BH5" s="56">
@@ -5731,44 +5724,44 @@
         <f>D21*10^-3</f>
         <v>9.6726917441917408E-4</v>
       </c>
-      <c r="BJ5" s="86">
+      <c r="BJ5" s="71">
         <f>E21*10^-3</f>
         <v>2.3991469043145797E-2</v>
       </c>
-      <c r="BK5" s="86">
+      <c r="BK5" s="71">
         <f>F21*10^-3</f>
         <v>1.0661672525943001E-3</v>
       </c>
       <c r="BM5" s="55">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="BN5" s="55">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.05</v>
       </c>
       <c r="BO5" s="50">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.9153556418772019E-2</v>
       </c>
       <c r="BP5" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.1678997816324404E-4</v>
       </c>
       <c r="BQ5" s="50">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.4107779909963638E-2</v>
       </c>
       <c r="BR5" s="50">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.7696462759186115E-3</v>
       </c>
       <c r="BS5" s="22">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.3607605538455468E-2</v>
       </c>
       <c r="BT5" s="22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.5067577430882933E-3</v>
       </c>
     </row>
@@ -5811,7 +5804,7 @@
         <f>C24*10^-3</f>
         <v>1.4295788703025902E-2</v>
       </c>
-      <c r="X6" s="86">
+      <c r="X6" s="71">
         <f>E24*10^-3</f>
         <v>2.4005844047446101E-2</v>
       </c>
@@ -5832,83 +5825,83 @@
         <v>1.7477286396192699E-3</v>
       </c>
       <c r="AG6" s="55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.05</v>
       </c>
       <c r="AH6" s="55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
       <c r="AI6" s="50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.9271425570780515E-2</v>
       </c>
       <c r="AJ6" s="50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1895941710358335E-4</v>
       </c>
       <c r="AK6" s="50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.4201888511290046E-2</v>
       </c>
       <c r="AL6" s="50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.7139615662387711E-3</v>
       </c>
       <c r="AM6" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.372390894330283E-2</v>
       </c>
       <c r="AN6" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7197649813853618E-3</v>
       </c>
       <c r="AR6" s="56">
-        <f>C16*10^-3</f>
+        <f t="shared" si="25"/>
         <v>1.47522399847013E-2</v>
       </c>
       <c r="AS6" s="56">
-        <f>D16*10^-3</f>
+        <f t="shared" si="25"/>
         <v>1.5544896639771899E-3</v>
       </c>
       <c r="AT6" s="56">
-        <f>E16*10^-3</f>
+        <f t="shared" si="25"/>
         <v>2.5586551655522899E-2</v>
       </c>
       <c r="AU6" s="56">
-        <f>F16*10^-3</f>
+        <f t="shared" si="25"/>
         <v>1.65576994046706E-3</v>
       </c>
       <c r="AW6" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.75</v>
       </c>
       <c r="AX6" s="55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
       <c r="AY6" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0027452933724342E-2</v>
       </c>
       <c r="AZ6" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3351635289149559E-4</v>
       </c>
       <c r="BA6" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.5137816933931016E-2</v>
       </c>
       <c r="BB6" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9091648303945254E-3</v>
       </c>
       <c r="BC6" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.5177166829034536E-2</v>
       </c>
       <c r="BD6" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.3084139899576663E-3</v>
       </c>
       <c r="BH6" s="56">
@@ -5919,44 +5912,44 @@
         <f>D24*10^-3</f>
         <v>9.5743396407127306E-4</v>
       </c>
-      <c r="BJ6" s="86">
+      <c r="BJ6" s="71">
         <f>E24*10^-3</f>
         <v>2.4005844047446101E-2</v>
       </c>
-      <c r="BK6" s="86">
+      <c r="BK6" s="71">
         <f>F24*10^-3</f>
         <v>1.06098217897798E-3</v>
       </c>
       <c r="BM6" s="55">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.3499999999999996</v>
       </c>
       <c r="BN6" s="55">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.05</v>
       </c>
       <c r="BO6" s="50">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.8595023226764654E-2</v>
       </c>
       <c r="BP6" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.0686794957910707E-4</v>
       </c>
       <c r="BQ6" s="50">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.4360023949956136E-2</v>
       </c>
       <c r="BR6" s="50">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.9027311987591693E-3</v>
       </c>
       <c r="BS6" s="22">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.3621750542686965E-2</v>
       </c>
       <c r="BT6" s="22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.6031565596175439E-3</v>
       </c>
     </row>
@@ -5999,7 +5992,7 @@
         <f>C26*10^-3</f>
         <v>1.3857623040785499E-2</v>
       </c>
-      <c r="X7" s="86">
+      <c r="X7" s="71">
         <f>E26*10^-3</f>
         <v>2.2961419711043599E-2</v>
       </c>
@@ -6020,27 +6013,27 @@
         <v>1.6759499431585601E-3</v>
       </c>
       <c r="AG7" s="55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.3499999999999996</v>
       </c>
       <c r="AH7" s="55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
       <c r="AI7" s="50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.8595023226764654E-2</v>
       </c>
       <c r="AJ7" s="50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0686794957910707E-4</v>
       </c>
       <c r="AK7" s="50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1689400906999563E-2</v>
       </c>
       <c r="AL7" s="50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.5966063620049638E-3</v>
       </c>
       <c r="AM7" s="22">
@@ -6048,7 +6041,7 @@
         <v>2.1002789783918323E-2</v>
       </c>
       <c r="AN7" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.6491347440680234E-3</v>
       </c>
       <c r="AR7" s="56">
@@ -6068,35 +6061,35 @@
         <v>1.67317466996315E-3</v>
       </c>
       <c r="AW7" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="AX7" s="55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
       <c r="AY7" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.939149791981681E-2</v>
       </c>
       <c r="AZ7" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.2119686199885508E-4</v>
       </c>
       <c r="BA7" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4128368674025288E-2</v>
       </c>
       <c r="BB7" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.6033686243128684E-3</v>
       </c>
       <c r="BC7" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.3918751436287296E-2</v>
       </c>
       <c r="BD7" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.1212060173397269E-3</v>
       </c>
       <c r="BH7" s="56">
@@ -6107,56 +6100,56 @@
         <f>D26*10^-3</f>
         <v>9.6053842000012608E-4</v>
       </c>
-      <c r="BJ7" s="86">
+      <c r="BJ7" s="71">
         <f>E26*10^-3</f>
         <v>2.2961419711043599E-2</v>
       </c>
-      <c r="BK7" s="86">
+      <c r="BK7" s="71">
         <f>F26*10^-3</f>
         <v>1.0503465778014301E-3</v>
       </c>
       <c r="BM7" s="55">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.5</v>
       </c>
       <c r="BN7" s="55">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.05</v>
       </c>
       <c r="BO7" s="50">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.8282479568623063E-2</v>
       </c>
       <c r="BP7" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.0156933093679474E-4</v>
       </c>
       <c r="BQ7" s="50">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.3613389661498493E-2</v>
       </c>
       <c r="BR7" s="50">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.2919270821457425E-3</v>
       </c>
       <c r="BS7" s="22">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.2594036995666904E-2</v>
       </c>
       <c r="BT7" s="22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.9344783070420393E-3</v>
       </c>
     </row>
     <row r="8" spans="1:72">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
       <c r="I8" s="55">
         <v>4.5</v>
       </c>
@@ -6206,7 +6199,7 @@
         <v>4.5</v>
       </c>
       <c r="AH8" s="55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
       <c r="AI8" s="50">
@@ -6214,15 +6207,15 @@
         <v>1.8282479568623063E-2</v>
       </c>
       <c r="AJ8" s="50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0156933093679474E-4</v>
       </c>
       <c r="AK8" s="50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1560562301079611E-2</v>
       </c>
       <c r="AL8" s="50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1760883981177758E-3</v>
       </c>
       <c r="AM8" s="22">
@@ -6230,7 +6223,7 @@
         <v>2.1212756352045666E-2</v>
       </c>
       <c r="AN8" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.3925362522927609E-3</v>
       </c>
       <c r="AR8" s="56">
@@ -6258,51 +6251,51 @@
         <v>0.05</v>
       </c>
       <c r="AY8" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8924164234530555E-2</v>
       </c>
       <c r="AZ8" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1264383472934852E-4</v>
       </c>
       <c r="BA8" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.3853601450756171E-2</v>
       </c>
       <c r="BB8" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.4796314728046387E-3</v>
       </c>
       <c r="BC8" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.320785105844763E-2</v>
       </c>
       <c r="BD8" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.5521331372709819E-3</v>
       </c>
-      <c r="BH8" s="95"/>
-      <c r="BI8" s="95"/>
-      <c r="BJ8" s="95"/>
-      <c r="BK8" s="95"/>
+      <c r="BH8" s="60"/>
+      <c r="BI8" s="60"/>
+      <c r="BJ8" s="60"/>
+      <c r="BK8" s="60"/>
     </row>
     <row r="9" spans="1:72">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="76" t="s">
+      <c r="C9" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="66" t="s">
         <v>92</v>
       </c>
       <c r="O9" s="55">
@@ -6340,11 +6333,11 @@
         <v>4.55</v>
       </c>
       <c r="AX9" s="55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
       <c r="AY9" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8181748887077825E-2</v>
       </c>
       <c r="AZ9" s="50">
@@ -6352,63 +6345,63 @@
         <v>9.9899719159768358E-5</v>
       </c>
       <c r="BA9" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.0421794413363857E-2</v>
       </c>
       <c r="BB9" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.2459260978402182E-3</v>
       </c>
       <c r="BC9" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9697537279304227E-2</v>
       </c>
       <c r="BD9" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.4794459496423483E-3</v>
       </c>
-      <c r="BH9" s="95"/>
-      <c r="BI9" s="95"/>
-      <c r="BJ9" s="95"/>
-      <c r="BK9" s="95"/>
+      <c r="BH9" s="60"/>
+      <c r="BI9" s="60"/>
+      <c r="BJ9" s="60"/>
+      <c r="BK9" s="60"/>
     </row>
     <row r="10" spans="1:72">
-      <c r="A10" s="77">
+      <c r="A10" s="67">
         <v>2900</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="67">
         <v>14.132897524374499</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="67">
         <v>1.6132140106919</v>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="67">
         <v>24.5109397376423</v>
       </c>
-      <c r="F10" s="77">
+      <c r="F10" s="67">
         <v>1.82238327806422</v>
       </c>
     </row>
     <row r="11" spans="1:72">
-      <c r="A11" s="77">
+      <c r="A11" s="67">
         <v>3200</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="77">
+      <c r="C11" s="67">
         <v>15.7321625477409</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="67">
         <v>1.62097280861413</v>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="67">
         <v>27.627634215834401</v>
       </c>
-      <c r="F11" s="77">
+      <c r="F11" s="67">
         <v>1.67735020829843</v>
       </c>
       <c r="AB11" s="51" t="s">
@@ -6420,28 +6413,28 @@
       <c r="AD11" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="AF11" s="88" t="s">
+      <c r="AF11" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="AG11" s="87" t="s">
+      <c r="AG11" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="AH11" s="87" t="s">
+      <c r="AH11" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="AI11" s="88" t="s">
+      <c r="AI11" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="AK11" s="88" t="s">
+      <c r="AK11" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="AL11" s="87" t="s">
+      <c r="AL11" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="AM11" s="87" t="s">
+      <c r="AM11" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="AN11" s="88" t="s">
+      <c r="AN11" s="73" t="s">
         <v>107</v>
       </c>
       <c r="AR11" s="51" t="s">
@@ -6453,28 +6446,28 @@
       <c r="AT11" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="AV11" s="88" t="s">
+      <c r="AV11" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="AW11" s="87" t="s">
+      <c r="AW11" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="AX11" s="87" t="s">
+      <c r="AX11" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="AY11" s="88" t="s">
+      <c r="AY11" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="BA11" s="88" t="s">
+      <c r="BA11" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="BB11" s="87" t="s">
+      <c r="BB11" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="BC11" s="87" t="s">
+      <c r="BC11" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="BD11" s="88" t="s">
+      <c r="BD11" s="73" t="s">
         <v>107</v>
       </c>
       <c r="BH11" s="51" t="s">
@@ -6486,48 +6479,48 @@
       <c r="BJ11" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="BL11" s="99" t="s">
+      <c r="BL11" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="BM11" s="100" t="s">
+      <c r="BM11" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="BN11" s="100" t="s">
+      <c r="BN11" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="BO11" s="99" t="s">
+      <c r="BO11" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="BQ11" s="99" t="s">
+      <c r="BQ11" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="BR11" s="100" t="s">
+      <c r="BR11" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="BS11" s="100" t="s">
+      <c r="BS11" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="BT11" s="99" t="s">
+      <c r="BT11" s="78" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:72">
-      <c r="A12" s="77">
+      <c r="A12" s="67">
         <v>3300</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="67">
         <v>15.625893748029901</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="67">
         <v>1.6937381733540999</v>
       </c>
-      <c r="E12" s="77">
+      <c r="E12" s="67">
         <v>24.358215545555002</v>
       </c>
-      <c r="F12" s="77">
+      <c r="F12" s="67">
         <v>4.6691997856601297</v>
       </c>
       <c r="AB12" s="50">
@@ -6664,756 +6657,749 @@
       </c>
     </row>
     <row r="13" spans="1:72">
-      <c r="A13" s="77">
+      <c r="A13" s="67">
         <v>3400</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="67">
         <v>15.421207002041299</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="67">
         <v>0.75790923401883004</v>
       </c>
-      <c r="E13" s="77">
+      <c r="E13" s="67">
         <v>27.434546940849302</v>
       </c>
-      <c r="F13" s="77">
+      <c r="F13" s="67">
         <v>1.0732065597335601</v>
       </c>
       <c r="AB13" s="50">
-        <f t="shared" ref="AB13:AB17" si="24">($A$3)/(SQRT(2*$C$3*$B$3*I4*10^3))</f>
+        <f t="shared" ref="AB13:AB17" si="26">($A$3)/(SQRT(2*$C$3*$B$3*I4*10^3))</f>
         <v>2.0440433556346103E-11</v>
       </c>
       <c r="AC13" s="50">
-        <f t="shared" ref="AC13:AC17" si="25">($A$3)/SQRT(8*$B$3*$C$3)*(I4*10^3)^(-3/2)</f>
+        <f t="shared" ref="AC13:AC17" si="27">($A$3)/SQRT(8*$B$3*$C$3)*(I4*10^3)^(-3/2)</f>
         <v>2.8389491050480746E-15</v>
       </c>
       <c r="AD13" s="50">
-        <f t="shared" ref="AD13:AD17" si="26">AC13*(J4*10^3)</f>
+        <f t="shared" ref="AD13:AD17" si="28">AC13*(J4*10^3)</f>
         <v>1.4194745525240373E-13</v>
       </c>
       <c r="AF13" s="1">
-        <f t="shared" ref="AF13:AF17" si="27">($D$3*AB4)/$F$3</f>
+        <f t="shared" ref="AF13:AF17" si="29">($D$3*AB4)/$F$3</f>
         <v>2.4327734448879724E-11</v>
       </c>
       <c r="AG13" s="50">
-        <f t="shared" ref="AG13:AG17" si="28">$D$3/$F$3</f>
+        <f t="shared" ref="AG13:AG17" si="30">$D$3/$F$3</f>
         <v>1.7040000000000001E-9</v>
       </c>
       <c r="AH13" s="50">
-        <f t="shared" ref="AH13:AH17" si="29">($D$3*AB4)/($F$3^2)</f>
+        <f t="shared" ref="AH13:AH17" si="31">($D$3*AB4)/($F$3^2)</f>
         <v>1.9462187559103779E-10</v>
       </c>
       <c r="AI13" s="1">
-        <f t="shared" ref="AI13:AI17" si="30">SQRT((AG13*AC4)^2+(AH13*G4)^2)</f>
+        <f t="shared" ref="AI13:AI17" si="32">SQRT((AG13*AC4)^2+(AH13*G4)^2)</f>
         <v>2.7169224760350294E-12</v>
       </c>
       <c r="AK13" s="1">
-        <f t="shared" ref="AK13:AK17" si="31">($E$3*AD4)/$F$3</f>
+        <f t="shared" ref="AK13:AK17" si="33">($E$3*AD4)/$F$3</f>
         <v>2.4177137302656768E-11</v>
       </c>
       <c r="AL13" s="50">
-        <f t="shared" ref="AL13:AL17" si="32">$E$3/$F$3</f>
+        <f t="shared" ref="AL13:AL17" si="34">$E$3/$F$3</f>
         <v>9.8400000000000012E-10</v>
       </c>
       <c r="AM13" s="50">
-        <f t="shared" ref="AM13:AM17" si="33">($E$3*AD4)/($F$3^2)</f>
+        <f t="shared" ref="AM13:AM17" si="35">($E$3*AD4)/($F$3^2)</f>
         <v>1.9341709842125414E-10</v>
       </c>
       <c r="AN13" s="1">
-        <f t="shared" ref="AN13:AN17" si="34">SQRT((AL13*AE4)^2+(AM13*G4)^2)</f>
+        <f t="shared" ref="AN13:AN17" si="36">SQRT((AL13*AE4)^2+(AM13*G4)^2)</f>
         <v>1.7505078547097955E-12</v>
       </c>
       <c r="AR13" s="50">
-        <f t="shared" ref="AR13:AR18" si="35">($A$3)/(SQRT(2*$C$3*$B$3*O4*10^3))</f>
+        <f t="shared" ref="AR13:AR18" si="37">($A$3)/(SQRT(2*$C$3*$B$3*O4*10^3))</f>
         <v>2.1680353767128075E-11</v>
       </c>
       <c r="AS13" s="50">
-        <f t="shared" ref="AS13:AS18" si="36">($A$3)/SQRT(8*$B$3*$C$3)*(O4*10^3)^(-3/2)</f>
+        <f t="shared" ref="AS13:AS17" si="38">($A$3)/SQRT(8*$B$3*$C$3)*(O4*10^3)^(-3/2)</f>
         <v>3.3875552761137574E-15</v>
       </c>
       <c r="AT13" s="50">
-        <f t="shared" ref="AT13:AT18" si="37">AS13*(P4*10^3)</f>
+        <f t="shared" ref="AT13:AT17" si="39">AS13*(P4*10^3)</f>
         <v>1.6937776380568786E-13</v>
       </c>
       <c r="AV13" s="1">
-        <f t="shared" ref="AV13:AV18" si="38">($D$3*AR4)/$F$3</f>
+        <f t="shared" ref="AV13:AV18" si="40">($D$3*AR4)/$F$3</f>
         <v>2.6807604981350498E-11</v>
       </c>
       <c r="AW13" s="50">
-        <f t="shared" ref="AW13:AW18" si="39">$D$3/$F$3</f>
+        <f t="shared" ref="AW13:AW18" si="41">$D$3/$F$3</f>
         <v>1.7040000000000001E-9</v>
       </c>
       <c r="AX13" s="50">
-        <f t="shared" ref="AX13:AX18" si="40">($D$3*AR4)/($F$3^2)</f>
+        <f t="shared" ref="AX13:AX18" si="42">($D$3*AR4)/($F$3^2)</f>
         <v>2.1446083985080399E-10</v>
       </c>
       <c r="AY13" s="1">
-        <f t="shared" ref="AY13:AY18" si="41">SQRT((AW13*AS4)^2+(AX13*W4)^2)</f>
+        <f t="shared" ref="AY13:AY18" si="43">SQRT((AW13*AS4)^2+(AX13*W4)^2)</f>
         <v>4.2136793498428473E-12</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" ref="BA13:BA18" si="42">($E$3*AT4)/$F$3</f>
+        <f t="shared" ref="BA13:BA18" si="44">($E$3*AT4)/$F$3</f>
         <v>2.7185592068381054E-11</v>
       </c>
       <c r="BB13" s="50">
-        <f t="shared" ref="BB13:BB18" si="43">$E$3/$F$3</f>
+        <f t="shared" ref="BB13:BB18" si="45">$E$3/$F$3</f>
         <v>9.8400000000000012E-10</v>
       </c>
       <c r="BC13" s="50">
-        <f t="shared" ref="BC13:BC18" si="44">($E$3*AT4)/($F$3^2)</f>
+        <f t="shared" ref="BC13:BC18" si="46">($E$3*AT4)/($F$3^2)</f>
         <v>2.1748473654704843E-10</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" ref="BD13:BD18" si="45">SQRT((BB13*AU4)^2+(BC13*W4)^2)</f>
+        <f t="shared" ref="BD13:BD17" si="47">SQRT((BB13*AU4)^2+(BC13*W4)^2)</f>
         <v>3.6245604492897296E-12</v>
       </c>
       <c r="BH13" s="50">
-        <f t="shared" ref="BH13:BH16" si="46">($A$3)/(SQRT(2*$C$3*$B$3*U4*10^3))</f>
+        <f t="shared" ref="BH13:BH16" si="48">($A$3)/(SQRT(2*$C$3*$B$3*U4*10^3))</f>
         <v>1.9895257080236344E-11</v>
       </c>
       <c r="BI13" s="50">
-        <f t="shared" ref="BI13:BI16" si="47">($A$3)/SQRT(8*$B$3*$C$3)*(U4*10^3)^(-3/2)</f>
+        <f t="shared" ref="BI13:BI16" si="49">($A$3)/SQRT(8*$B$3*$C$3)*(U4*10^3)^(-3/2)</f>
         <v>2.6177969842416209E-15</v>
       </c>
       <c r="BJ13" s="50">
-        <f t="shared" ref="BJ13:BJ16" si="48">BI13*(V4*10^3)</f>
+        <f t="shared" ref="BJ13:BJ16" si="50">BI13*(V4*10^3)</f>
         <v>1.3088984921208103E-13</v>
       </c>
       <c r="BL13" s="22">
-        <f t="shared" ref="BL13:BL17" si="49">($D$3*BH4)/$F$3</f>
+        <f t="shared" ref="BL13:BL16" si="51">($D$3*BH4)/$F$3</f>
         <v>2.5283307346650445E-11</v>
       </c>
       <c r="BM13" s="50">
-        <f t="shared" ref="BM13:BM17" si="50">$D$3/$F$3</f>
+        <f t="shared" ref="BM13:BM16" si="52">$D$3/$F$3</f>
         <v>1.7040000000000001E-9</v>
       </c>
       <c r="BN13" s="50">
-        <f t="shared" ref="BN13:BN17" si="51">($D$3*BH4)/($F$3^2)</f>
+        <f t="shared" ref="BN13:BN16" si="53">($D$3*BH4)/($F$3^2)</f>
         <v>2.0226645877320356E-10</v>
       </c>
       <c r="BO13" s="22">
-        <f t="shared" ref="BO13:BO17" si="52">SQRT((BM13*BI4)^2+(BN13*AM4)^2)</f>
+        <f t="shared" ref="BO13:BO16" si="54">SQRT((BM13*BI4)^2+(BN13*AM4)^2)</f>
         <v>5.112744965298272E-12</v>
       </c>
       <c r="BQ13" s="22">
-        <f t="shared" ref="BQ13:BQ17" si="53">($E$3*BJ4)/$F$3</f>
+        <f t="shared" ref="BQ13:BQ16" si="55">($E$3*BJ4)/$F$3</f>
         <v>2.4650846668149935E-11</v>
       </c>
       <c r="BR13" s="50">
-        <f t="shared" ref="BR13:BR17" si="54">$E$3/$F$3</f>
+        <f t="shared" ref="BR13:BR16" si="56">$E$3/$F$3</f>
         <v>9.8400000000000012E-10</v>
       </c>
       <c r="BS13" s="50">
-        <f t="shared" ref="BS13:BS17" si="55">($E$3*BJ4)/($F$3^2)</f>
+        <f t="shared" ref="BS13:BS16" si="57">($E$3*BJ4)/($F$3^2)</f>
         <v>1.9720677334519948E-10</v>
       </c>
       <c r="BT13" s="22">
-        <f t="shared" ref="BT13:BT17" si="56">SQRT((BR13*BK4)^2+(BS13*AM4)^2)</f>
+        <f t="shared" ref="BT13:BT16" si="58">SQRT((BR13*BK4)^2+(BS13*AM4)^2)</f>
         <v>4.8866036900283695E-12</v>
       </c>
     </row>
     <row r="14" spans="1:72">
-      <c r="A14" s="77">
+      <c r="A14" s="67">
         <v>3600</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="67">
         <v>14.276839465305001</v>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="67">
         <v>1.5944380727905101</v>
       </c>
-      <c r="E14" s="77">
+      <c r="E14" s="67">
         <v>24.570261486439801</v>
       </c>
-      <c r="F14" s="77">
+      <c r="F14" s="67">
         <v>1.7789713970628001</v>
       </c>
       <c r="AB14" s="50">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1.9638533330119516E-11</v>
       </c>
       <c r="AC14" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2.5177606833486581E-15</v>
       </c>
       <c r="AD14" s="50">
+        <f t="shared" si="28"/>
+        <v>1.2588803416743291E-13</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" si="29"/>
+        <v>2.3674067261908316E-11</v>
+      </c>
+      <c r="AG14" s="50">
+        <f t="shared" si="30"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="AH14" s="50">
+        <f t="shared" si="31"/>
+        <v>1.8939253809526653E-10</v>
+      </c>
+      <c r="AI14" s="1">
+        <f t="shared" si="32"/>
+        <v>2.7001474234302577E-12</v>
+      </c>
+      <c r="AK14" s="1">
+        <f t="shared" si="33"/>
+        <v>2.3207290010348055E-11</v>
+      </c>
+      <c r="AL14" s="50">
+        <f t="shared" si="34"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="AM14" s="50">
+        <f t="shared" si="35"/>
+        <v>1.8565832008278444E-10</v>
+      </c>
+      <c r="AN14" s="1">
+        <f t="shared" si="36"/>
+        <v>1.6783379809337922E-12</v>
+      </c>
+      <c r="AR14" s="50">
+        <f t="shared" si="37"/>
+        <v>2.0440433556346103E-11</v>
+      </c>
+      <c r="AS14" s="50">
+        <f t="shared" si="38"/>
+        <v>2.8389491050480746E-15</v>
+      </c>
+      <c r="AT14" s="50">
+        <f t="shared" si="39"/>
+        <v>1.4194745525240373E-13</v>
+      </c>
+      <c r="AV14" s="1">
+        <f t="shared" si="40"/>
+        <v>2.4892388903797864E-11</v>
+      </c>
+      <c r="AW14" s="50">
+        <f t="shared" si="41"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="AX14" s="50">
+        <f t="shared" si="42"/>
+        <v>1.9913911123038291E-10</v>
+      </c>
+      <c r="AY14" s="1">
+        <f t="shared" si="43"/>
+        <v>3.9853698544285529E-12</v>
+      </c>
+      <c r="BA14" s="1">
+        <f t="shared" si="44"/>
+        <v>2.4875955336248612E-11</v>
+      </c>
+      <c r="BB14" s="50">
+        <f t="shared" si="45"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="BC14" s="50">
+        <f t="shared" si="46"/>
+        <v>1.990076426899889E-10</v>
+      </c>
+      <c r="BD14" s="1">
+        <f t="shared" si="47"/>
+        <v>3.3118567217586101E-12</v>
+      </c>
+      <c r="BH14" s="50">
+        <f t="shared" si="48"/>
+        <v>1.9153556418772018E-11</v>
+      </c>
+      <c r="BI14" s="50">
+        <f t="shared" si="49"/>
+        <v>2.335799563264881E-15</v>
+      </c>
+      <c r="BJ14" s="50">
+        <f t="shared" si="50"/>
+        <v>1.1678997816324404E-13</v>
+      </c>
+      <c r="BL14" s="22">
+        <f t="shared" si="51"/>
+        <v>2.4107779909963639E-11</v>
+      </c>
+      <c r="BM14" s="50">
+        <f t="shared" si="52"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="BN14" s="50">
+        <f t="shared" si="53"/>
+        <v>1.9286223927970911E-10</v>
+      </c>
+      <c r="BO14" s="22">
+        <f t="shared" si="54"/>
+        <v>4.7696462759186118E-12</v>
+      </c>
+      <c r="BQ14" s="22">
+        <f t="shared" si="55"/>
+        <v>2.3607605538455469E-11</v>
+      </c>
+      <c r="BR14" s="50">
+        <f t="shared" si="56"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="BS14" s="50">
+        <f t="shared" si="57"/>
+        <v>1.8886084430764375E-10</v>
+      </c>
+      <c r="BT14" s="22">
+        <f t="shared" si="58"/>
+        <v>4.5067577430882929E-12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:72">
+      <c r="A15" s="67">
+        <v>3600</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="67">
+        <v>14.608209450585599</v>
+      </c>
+      <c r="D15" s="67">
+        <v>1.65422061844574</v>
+      </c>
+      <c r="E15" s="67">
+        <v>25.280442414886799</v>
+      </c>
+      <c r="F15" s="67">
+        <v>1.7722852073505899</v>
+      </c>
+      <c r="AB15" s="50">
         <f t="shared" si="26"/>
-        <v>1.2588803416743291E-13</v>
-      </c>
-      <c r="AF14" s="1">
+        <v>1.9271425570780514E-11</v>
+      </c>
+      <c r="AC15" s="50">
         <f t="shared" si="27"/>
-        <v>2.3674067261908316E-11</v>
-      </c>
-      <c r="AG14" s="50">
+        <v>2.3791883420716669E-15</v>
+      </c>
+      <c r="AD15" s="50">
         <f t="shared" si="28"/>
+        <v>1.1895941710358335E-13</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="29"/>
+        <v>2.4201888511290045E-11</v>
+      </c>
+      <c r="AG15" s="50">
+        <f t="shared" si="30"/>
         <v>1.7040000000000001E-9</v>
       </c>
-      <c r="AH14" s="50">
+      <c r="AH15" s="50">
+        <f t="shared" si="31"/>
+        <v>1.9361510809032036E-10</v>
+      </c>
+      <c r="AI15" s="1">
+        <f t="shared" si="32"/>
+        <v>2.7139615662387711E-12</v>
+      </c>
+      <c r="AK15" s="1">
+        <f t="shared" si="33"/>
+        <v>2.3723908943302832E-11</v>
+      </c>
+      <c r="AL15" s="50">
+        <f t="shared" si="34"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="AM15" s="50">
+        <f t="shared" si="35"/>
+        <v>1.8979127154642265E-10</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="36"/>
+        <v>1.7197649813853617E-12</v>
+      </c>
+      <c r="AR15" s="50">
+        <f t="shared" si="37"/>
+        <v>2.0027452933724342E-11</v>
+      </c>
+      <c r="AS15" s="50">
+        <f t="shared" si="38"/>
+        <v>2.6703270578299118E-15</v>
+      </c>
+      <c r="AT15" s="50">
+        <f t="shared" si="39"/>
+        <v>1.3351635289149559E-13</v>
+      </c>
+      <c r="AV15" s="1">
+        <f t="shared" si="40"/>
+        <v>2.5137816933931016E-11</v>
+      </c>
+      <c r="AW15" s="50">
+        <f t="shared" si="41"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="AX15" s="50">
+        <f t="shared" si="42"/>
+        <v>2.0110253547144813E-10</v>
+      </c>
+      <c r="AY15" s="1">
+        <f t="shared" si="43"/>
+        <v>3.9091648303945256E-12</v>
+      </c>
+      <c r="BA15" s="1">
+        <f t="shared" si="44"/>
+        <v>2.5177166829034537E-11</v>
+      </c>
+      <c r="BB15" s="50">
+        <f t="shared" si="45"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="BC15" s="50">
+        <f t="shared" si="46"/>
+        <v>2.014173346322763E-10</v>
+      </c>
+      <c r="BD15" s="1">
+        <f t="shared" si="47"/>
+        <v>3.3084139899576662E-12</v>
+      </c>
+      <c r="BH15" s="50">
+        <f t="shared" si="48"/>
+        <v>1.8595023226764655E-11</v>
+      </c>
+      <c r="BI15" s="50">
+        <f t="shared" si="49"/>
+        <v>2.1373589915821413E-15</v>
+      </c>
+      <c r="BJ15" s="50">
+        <f t="shared" si="50"/>
+        <v>1.0686794957910707E-13</v>
+      </c>
+      <c r="BL15" s="22">
+        <f t="shared" si="51"/>
+        <v>2.4360023949956137E-11</v>
+      </c>
+      <c r="BM15" s="50">
+        <f t="shared" si="52"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="BN15" s="50">
+        <f t="shared" si="53"/>
+        <v>1.9488019159964909E-10</v>
+      </c>
+      <c r="BO15" s="22">
+        <f t="shared" si="54"/>
+        <v>4.9027311987591696E-12</v>
+      </c>
+      <c r="BQ15" s="22">
+        <f t="shared" si="55"/>
+        <v>2.3621750542686966E-11</v>
+      </c>
+      <c r="BR15" s="50">
+        <f t="shared" si="56"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="BS15" s="50">
+        <f t="shared" si="57"/>
+        <v>1.8897400434149573E-10</v>
+      </c>
+      <c r="BT15" s="22">
+        <f t="shared" si="58"/>
+        <v>4.6031565596175437E-12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:72">
+      <c r="A16" s="67">
+        <v>3750</v>
+      </c>
+      <c r="B16" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="67">
+        <v>14.752239984701299</v>
+      </c>
+      <c r="D16" s="67">
+        <v>1.5544896639771899</v>
+      </c>
+      <c r="E16" s="67">
+        <v>25.5865516555229</v>
+      </c>
+      <c r="F16" s="67">
+        <v>1.6557699404670601</v>
+      </c>
+      <c r="AB16" s="50">
+        <f t="shared" si="26"/>
+        <v>1.8595023226764655E-11</v>
+      </c>
+      <c r="AC16" s="50">
+        <f t="shared" si="27"/>
+        <v>2.1373589915821413E-15</v>
+      </c>
+      <c r="AD16" s="50">
+        <f t="shared" si="28"/>
+        <v>1.0686794957910707E-13</v>
+      </c>
+      <c r="AF16" s="1">
         <f t="shared" si="29"/>
-        <v>1.8939253809526653E-10</v>
-      </c>
-      <c r="AI14" s="1">
+        <v>2.1689400906999562E-11</v>
+      </c>
+      <c r="AG16" s="50">
         <f t="shared" si="30"/>
-        <v>2.7001474234302577E-12</v>
-      </c>
-      <c r="AK14" s="1">
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="AH16" s="50">
         <f t="shared" si="31"/>
-        <v>2.3207290010348055E-11</v>
-      </c>
-      <c r="AL14" s="50">
+        <v>1.7351520725599649E-10</v>
+      </c>
+      <c r="AI16" s="1">
         <f t="shared" si="32"/>
+        <v>2.5966063620049636E-12</v>
+      </c>
+      <c r="AK16" s="1">
+        <f t="shared" si="33"/>
+        <v>2.1002789783918323E-11</v>
+      </c>
+      <c r="AL16" s="50">
+        <f t="shared" si="34"/>
         <v>9.8400000000000012E-10</v>
       </c>
-      <c r="AM14" s="50">
+      <c r="AM16" s="50">
+        <f t="shared" si="35"/>
+        <v>1.6802231827134658E-10</v>
+      </c>
+      <c r="AN16" s="1">
+        <f t="shared" si="36"/>
+        <v>1.6491347440680233E-12</v>
+      </c>
+      <c r="AR16" s="50">
+        <f t="shared" si="37"/>
+        <v>1.939149791981681E-11</v>
+      </c>
+      <c r="AS16" s="50">
+        <f t="shared" si="38"/>
+        <v>2.4239372399771015E-15</v>
+      </c>
+      <c r="AT16" s="50">
+        <f t="shared" si="39"/>
+        <v>1.2119686199885508E-13</v>
+      </c>
+      <c r="AV16" s="1">
+        <f t="shared" si="40"/>
+        <v>2.4128368674025288E-11</v>
+      </c>
+      <c r="AW16" s="50">
+        <f t="shared" si="41"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="AX16" s="50">
+        <f t="shared" si="42"/>
+        <v>1.9302694939220231E-10</v>
+      </c>
+      <c r="AY16" s="1">
+        <f t="shared" si="43"/>
+        <v>3.6033686243128684E-12</v>
+      </c>
+      <c r="BA16" s="1">
+        <f t="shared" si="44"/>
+        <v>2.3918751436287295E-11</v>
+      </c>
+      <c r="BB16" s="50">
+        <f t="shared" si="45"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="BC16" s="50">
+        <f t="shared" si="46"/>
+        <v>1.9135001149029836E-10</v>
+      </c>
+      <c r="BD16" s="1">
+        <f t="shared" si="47"/>
+        <v>3.121206017339727E-12</v>
+      </c>
+      <c r="BH16" s="50">
+        <f t="shared" si="48"/>
+        <v>1.8282479568623062E-11</v>
+      </c>
+      <c r="BI16" s="50">
+        <f t="shared" si="49"/>
+        <v>2.0313866187358948E-15</v>
+      </c>
+      <c r="BJ16" s="50">
+        <f t="shared" si="50"/>
+        <v>1.0156933093679474E-13</v>
+      </c>
+      <c r="BL16" s="22">
+        <f t="shared" si="51"/>
+        <v>2.3613389661498492E-11</v>
+      </c>
+      <c r="BM16" s="50">
+        <f t="shared" si="52"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="BN16" s="50">
+        <f t="shared" si="53"/>
+        <v>1.8890711729198794E-10</v>
+      </c>
+      <c r="BO16" s="22">
+        <f t="shared" si="54"/>
+        <v>4.2919270821457425E-12</v>
+      </c>
+      <c r="BQ16" s="22">
+        <f t="shared" si="55"/>
+        <v>2.2594036995666905E-11</v>
+      </c>
+      <c r="BR16" s="50">
+        <f t="shared" si="56"/>
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="BS16" s="50">
+        <f t="shared" si="57"/>
+        <v>1.8075229596533524E-10</v>
+      </c>
+      <c r="BT16" s="22">
+        <f t="shared" si="58"/>
+        <v>3.9344783070420396E-12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:71">
+      <c r="A17" s="67">
+        <v>3800</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="67">
+        <v>14.837621682306599</v>
+      </c>
+      <c r="D17" s="67">
+        <v>0.87554886606265003</v>
+      </c>
+      <c r="E17" s="67">
+        <v>25.0516734432418</v>
+      </c>
+      <c r="F17" s="67">
+        <v>1.08795415484975</v>
+      </c>
+      <c r="AB17" s="50">
+        <f t="shared" si="26"/>
+        <v>1.8282479568623062E-11</v>
+      </c>
+      <c r="AC17" s="50">
+        <f t="shared" si="27"/>
+        <v>2.0313866187358948E-15</v>
+      </c>
+      <c r="AD17" s="50">
+        <f t="shared" si="28"/>
+        <v>1.0156933093679474E-13</v>
+      </c>
+      <c r="AF17" s="1">
+        <f t="shared" si="29"/>
+        <v>2.1560562301079612E-11</v>
+      </c>
+      <c r="AG17" s="50">
+        <f t="shared" si="30"/>
+        <v>1.7040000000000001E-9</v>
+      </c>
+      <c r="AH17" s="50">
+        <f t="shared" si="31"/>
+        <v>1.724844984086369E-10</v>
+      </c>
+      <c r="AI17" s="1">
+        <f t="shared" si="32"/>
+        <v>2.1760883981177757E-12</v>
+      </c>
+      <c r="AK17" s="1">
         <f t="shared" si="33"/>
-        <v>1.8565832008278444E-10</v>
-      </c>
-      <c r="AN14" s="1">
+        <v>2.1212756352045666E-11</v>
+      </c>
+      <c r="AL17" s="50">
         <f t="shared" si="34"/>
-        <v>1.6783379809337922E-12</v>
-      </c>
-      <c r="AR14" s="50">
+        <v>9.8400000000000012E-10</v>
+      </c>
+      <c r="AM17" s="50">
         <f t="shared" si="35"/>
-        <v>2.0440433556346103E-11</v>
-      </c>
-      <c r="AS14" s="50">
+        <v>1.6970205081636533E-10</v>
+      </c>
+      <c r="AN17" s="1">
         <f t="shared" si="36"/>
-        <v>2.8389491050480746E-15</v>
-      </c>
-      <c r="AT14" s="50">
+        <v>1.392536252292761E-12</v>
+      </c>
+      <c r="AR17" s="50">
         <f t="shared" si="37"/>
-        <v>1.4194745525240373E-13</v>
-      </c>
-      <c r="AV14" s="1">
+        <v>1.8924164234530555E-11</v>
+      </c>
+      <c r="AS17" s="50">
         <f t="shared" si="38"/>
-        <v>2.4892388903797864E-11</v>
-      </c>
-      <c r="AW14" s="50">
+        <v>2.2528766945869704E-15</v>
+      </c>
+      <c r="AT17" s="50">
         <f t="shared" si="39"/>
+        <v>1.1264383472934852E-13</v>
+      </c>
+      <c r="AV17" s="1">
+        <f t="shared" si="40"/>
+        <v>2.3853601450756169E-11</v>
+      </c>
+      <c r="AW17" s="50">
+        <f t="shared" si="41"/>
         <v>1.7040000000000001E-9</v>
       </c>
-      <c r="AX14" s="50">
-        <f t="shared" si="40"/>
-        <v>1.9913911123038291E-10</v>
-      </c>
-      <c r="AY14" s="1">
-        <f t="shared" si="41"/>
-        <v>3.9853698544285529E-12</v>
-      </c>
-      <c r="BA14" s="1">
+      <c r="AX17" s="50">
         <f t="shared" si="42"/>
-        <v>2.4875955336248612E-11</v>
-      </c>
-      <c r="BB14" s="50">
+        <v>1.9082881160604935E-10</v>
+      </c>
+      <c r="AY17" s="1">
         <f t="shared" si="43"/>
+        <v>2.4796314728046389E-12</v>
+      </c>
+      <c r="BA17" s="1">
+        <f t="shared" si="44"/>
+        <v>2.3207851058447629E-11</v>
+      </c>
+      <c r="BB17" s="50">
+        <f t="shared" si="45"/>
         <v>9.8400000000000012E-10</v>
       </c>
-      <c r="BC14" s="50">
-        <f t="shared" si="44"/>
-        <v>1.990076426899889E-10</v>
-      </c>
-      <c r="BD14" s="1">
-        <f t="shared" si="45"/>
-        <v>3.3118567217586101E-12</v>
-      </c>
-      <c r="BH14" s="50">
+      <c r="BC17" s="50">
         <f t="shared" si="46"/>
-        <v>1.9153556418772018E-11</v>
-      </c>
-      <c r="BI14" s="50">
+        <v>1.8566280846758103E-10</v>
+      </c>
+      <c r="BD17" s="1">
         <f t="shared" si="47"/>
-        <v>2.335799563264881E-15</v>
-      </c>
-      <c r="BJ14" s="50">
-        <f t="shared" si="48"/>
-        <v>1.1678997816324404E-13</v>
-      </c>
-      <c r="BL14" s="22">
-        <f t="shared" si="49"/>
-        <v>2.4107779909963639E-11</v>
-      </c>
-      <c r="BM14" s="50">
-        <f t="shared" si="50"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="BN14" s="50">
-        <f t="shared" si="51"/>
-        <v>1.9286223927970911E-10</v>
-      </c>
-      <c r="BO14" s="22">
-        <f t="shared" si="52"/>
-        <v>4.7696462759186118E-12</v>
-      </c>
-      <c r="BQ14" s="22">
-        <f t="shared" si="53"/>
-        <v>2.3607605538455469E-11</v>
-      </c>
-      <c r="BR14" s="50">
-        <f t="shared" si="54"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="BS14" s="50">
-        <f t="shared" si="55"/>
-        <v>1.8886084430764375E-10</v>
-      </c>
-      <c r="BT14" s="22">
-        <f t="shared" si="56"/>
-        <v>4.5067577430882929E-12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:72">
-      <c r="A15" s="77">
-        <v>3600</v>
-      </c>
-      <c r="B15" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="77">
-        <v>14.608209450585599</v>
-      </c>
-      <c r="D15" s="77">
-        <v>1.65422061844574</v>
-      </c>
-      <c r="E15" s="77">
-        <v>25.280442414886799</v>
-      </c>
-      <c r="F15" s="77">
-        <v>1.7722852073505899</v>
-      </c>
-      <c r="AB15" s="50">
-        <f t="shared" si="24"/>
-        <v>1.9271425570780514E-11</v>
-      </c>
-      <c r="AC15" s="50">
-        <f t="shared" si="25"/>
-        <v>2.3791883420716669E-15</v>
-      </c>
-      <c r="AD15" s="50">
-        <f t="shared" si="26"/>
-        <v>1.1895941710358335E-13</v>
-      </c>
-      <c r="AF15" s="1">
-        <f t="shared" si="27"/>
-        <v>2.4201888511290045E-11</v>
-      </c>
-      <c r="AG15" s="50">
-        <f t="shared" si="28"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="AH15" s="50">
-        <f t="shared" si="29"/>
-        <v>1.9361510809032036E-10</v>
-      </c>
-      <c r="AI15" s="1">
-        <f t="shared" si="30"/>
-        <v>2.7139615662387711E-12</v>
-      </c>
-      <c r="AK15" s="1">
-        <f t="shared" si="31"/>
-        <v>2.3723908943302832E-11</v>
-      </c>
-      <c r="AL15" s="50">
-        <f t="shared" si="32"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="AM15" s="50">
-        <f t="shared" si="33"/>
-        <v>1.8979127154642265E-10</v>
-      </c>
-      <c r="AN15" s="1">
-        <f t="shared" si="34"/>
-        <v>1.7197649813853617E-12</v>
-      </c>
-      <c r="AR15" s="50">
-        <f t="shared" si="35"/>
-        <v>2.0027452933724342E-11</v>
-      </c>
-      <c r="AS15" s="50">
-        <f t="shared" si="36"/>
-        <v>2.6703270578299118E-15</v>
-      </c>
-      <c r="AT15" s="50">
+        <v>1.552133137270982E-12</v>
+      </c>
+      <c r="BH17" s="27"/>
+      <c r="BI17" s="27"/>
+      <c r="BJ17" s="27"/>
+      <c r="BM17" s="27"/>
+      <c r="BN17" s="27"/>
+      <c r="BR17" s="27"/>
+      <c r="BS17" s="27"/>
+    </row>
+    <row r="18" spans="1:71">
+      <c r="A18" s="67">
+        <v>3900</v>
+      </c>
+      <c r="B18" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="67">
+        <v>13.8932319612138</v>
+      </c>
+      <c r="D18" s="67">
+        <v>1.5845935583510899</v>
+      </c>
+      <c r="E18" s="67">
+        <v>23.5846443194594</v>
+      </c>
+      <c r="F18" s="67">
+        <v>1.7056280294042601</v>
+      </c>
+      <c r="AR18" s="50">
         <f t="shared" si="37"/>
-        <v>1.3351635289149559E-13</v>
-      </c>
-      <c r="AV15" s="1">
-        <f t="shared" si="38"/>
-        <v>2.5137816933931016E-11</v>
-      </c>
-      <c r="AW15" s="50">
-        <f t="shared" si="39"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="AX15" s="50">
-        <f t="shared" si="40"/>
-        <v>2.0110253547144813E-10</v>
-      </c>
-      <c r="AY15" s="1">
-        <f t="shared" si="41"/>
-        <v>3.9091648303945256E-12</v>
-      </c>
-      <c r="BA15" s="1">
-        <f t="shared" si="42"/>
-        <v>2.5177166829034537E-11</v>
-      </c>
-      <c r="BB15" s="50">
-        <f t="shared" si="43"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="BC15" s="50">
-        <f t="shared" si="44"/>
-        <v>2.014173346322763E-10</v>
-      </c>
-      <c r="BD15" s="1">
-        <f t="shared" si="45"/>
-        <v>3.3084139899576662E-12</v>
-      </c>
-      <c r="BH15" s="50">
-        <f t="shared" si="46"/>
-        <v>1.8595023226764655E-11</v>
-      </c>
-      <c r="BI15" s="50">
-        <f t="shared" si="47"/>
-        <v>2.1373589915821413E-15</v>
-      </c>
-      <c r="BJ15" s="50">
-        <f t="shared" si="48"/>
-        <v>1.0686794957910707E-13</v>
-      </c>
-      <c r="BL15" s="22">
-        <f t="shared" si="49"/>
-        <v>2.4360023949956137E-11</v>
-      </c>
-      <c r="BM15" s="50">
-        <f t="shared" si="50"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="BN15" s="50">
-        <f t="shared" si="51"/>
-        <v>1.9488019159964909E-10</v>
-      </c>
-      <c r="BO15" s="22">
-        <f t="shared" si="52"/>
-        <v>4.9027311987591696E-12</v>
-      </c>
-      <c r="BQ15" s="22">
-        <f t="shared" si="53"/>
-        <v>2.3621750542686966E-11</v>
-      </c>
-      <c r="BR15" s="50">
-        <f t="shared" si="54"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="BS15" s="50">
-        <f t="shared" si="55"/>
-        <v>1.8897400434149573E-10</v>
-      </c>
-      <c r="BT15" s="22">
-        <f t="shared" si="56"/>
-        <v>4.6031565596175437E-12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:72">
-      <c r="A16" s="77">
-        <v>3750</v>
-      </c>
-      <c r="B16" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="77">
-        <v>14.752239984701299</v>
-      </c>
-      <c r="D16" s="77">
-        <v>1.5544896639771899</v>
-      </c>
-      <c r="E16" s="77">
-        <v>25.5865516555229</v>
-      </c>
-      <c r="F16" s="77">
-        <v>1.6557699404670601</v>
-      </c>
-      <c r="AB16" s="50">
-        <f t="shared" si="24"/>
-        <v>1.8595023226764655E-11</v>
-      </c>
-      <c r="AC16" s="50">
-        <f t="shared" si="25"/>
-        <v>2.1373589915821413E-15</v>
-      </c>
-      <c r="AD16" s="50">
-        <f t="shared" si="26"/>
-        <v>1.0686794957910707E-13</v>
-      </c>
-      <c r="AF16" s="1">
-        <f t="shared" si="27"/>
-        <v>2.1689400906999562E-11</v>
-      </c>
-      <c r="AG16" s="50">
-        <f t="shared" si="28"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="AH16" s="50">
-        <f t="shared" si="29"/>
-        <v>1.7351520725599649E-10</v>
-      </c>
-      <c r="AI16" s="1">
-        <f t="shared" si="30"/>
-        <v>2.5966063620049636E-12</v>
-      </c>
-      <c r="AK16" s="1">
-        <f t="shared" si="31"/>
-        <v>2.1002789783918323E-11</v>
-      </c>
-      <c r="AL16" s="50">
-        <f t="shared" si="32"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="AM16" s="50">
-        <f t="shared" si="33"/>
-        <v>1.6802231827134658E-10</v>
-      </c>
-      <c r="AN16" s="1">
-        <f t="shared" si="34"/>
-        <v>1.6491347440680233E-12</v>
-      </c>
-      <c r="AR16" s="50">
-        <f t="shared" si="35"/>
-        <v>1.939149791981681E-11</v>
-      </c>
-      <c r="AS16" s="50">
-        <f t="shared" si="36"/>
-        <v>2.4239372399771015E-15</v>
-      </c>
-      <c r="AT16" s="50">
-        <f t="shared" si="37"/>
-        <v>1.2119686199885508E-13</v>
-      </c>
-      <c r="AV16" s="1">
-        <f t="shared" si="38"/>
-        <v>2.4128368674025288E-11</v>
-      </c>
-      <c r="AW16" s="50">
-        <f t="shared" si="39"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="AX16" s="50">
-        <f t="shared" si="40"/>
-        <v>1.9302694939220231E-10</v>
-      </c>
-      <c r="AY16" s="1">
-        <f t="shared" si="41"/>
-        <v>3.6033686243128684E-12</v>
-      </c>
-      <c r="BA16" s="1">
-        <f t="shared" si="42"/>
-        <v>2.3918751436287295E-11</v>
-      </c>
-      <c r="BB16" s="50">
-        <f t="shared" si="43"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="BC16" s="50">
-        <f t="shared" si="44"/>
-        <v>1.9135001149029836E-10</v>
-      </c>
-      <c r="BD16" s="1">
-        <f t="shared" si="45"/>
-        <v>3.121206017339727E-12</v>
-      </c>
-      <c r="BH16" s="50">
-        <f t="shared" si="46"/>
-        <v>1.8282479568623062E-11</v>
-      </c>
-      <c r="BI16" s="50">
-        <f t="shared" si="47"/>
-        <v>2.0313866187358948E-15</v>
-      </c>
-      <c r="BJ16" s="50">
-        <f t="shared" si="48"/>
-        <v>1.0156933093679474E-13</v>
-      </c>
-      <c r="BL16" s="22">
-        <f t="shared" si="49"/>
-        <v>2.3613389661498492E-11</v>
-      </c>
-      <c r="BM16" s="50">
-        <f t="shared" si="50"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="BN16" s="50">
-        <f t="shared" si="51"/>
-        <v>1.8890711729198794E-10</v>
-      </c>
-      <c r="BO16" s="22">
-        <f t="shared" si="52"/>
-        <v>4.2919270821457425E-12</v>
-      </c>
-      <c r="BQ16" s="22">
-        <f t="shared" si="53"/>
-        <v>2.2594036995666905E-11</v>
-      </c>
-      <c r="BR16" s="50">
-        <f t="shared" si="54"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="BS16" s="50">
-        <f t="shared" si="55"/>
-        <v>1.8075229596533524E-10</v>
-      </c>
-      <c r="BT16" s="22">
-        <f t="shared" si="56"/>
-        <v>3.9344783070420396E-12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:73">
-      <c r="A17" s="77">
-        <v>3800</v>
-      </c>
-      <c r="B17" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="77">
-        <v>14.837621682306599</v>
-      </c>
-      <c r="D17" s="77">
-        <v>0.87554886606265003</v>
-      </c>
-      <c r="E17" s="77">
-        <v>25.0516734432418</v>
-      </c>
-      <c r="F17" s="77">
-        <v>1.08795415484975</v>
-      </c>
-      <c r="AB17" s="50">
-        <f t="shared" si="24"/>
-        <v>1.8282479568623062E-11</v>
-      </c>
-      <c r="AC17" s="50">
-        <f t="shared" si="25"/>
-        <v>2.0313866187358948E-15</v>
-      </c>
-      <c r="AD17" s="50">
-        <f t="shared" si="26"/>
-        <v>1.0156933093679474E-13</v>
-      </c>
-      <c r="AF17" s="1">
-        <f t="shared" si="27"/>
-        <v>2.1560562301079612E-11</v>
-      </c>
-      <c r="AG17" s="50">
-        <f t="shared" si="28"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="AH17" s="50">
-        <f t="shared" si="29"/>
-        <v>1.724844984086369E-10</v>
-      </c>
-      <c r="AI17" s="1">
-        <f t="shared" si="30"/>
-        <v>2.1760883981177757E-12</v>
-      </c>
-      <c r="AK17" s="1">
-        <f t="shared" si="31"/>
-        <v>2.1212756352045666E-11</v>
-      </c>
-      <c r="AL17" s="50">
-        <f t="shared" si="32"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="AM17" s="50">
-        <f t="shared" si="33"/>
-        <v>1.6970205081636533E-10</v>
-      </c>
-      <c r="AN17" s="1">
-        <f t="shared" si="34"/>
-        <v>1.392536252292761E-12</v>
-      </c>
-      <c r="AR17" s="50">
-        <f t="shared" si="35"/>
-        <v>1.8924164234530555E-11</v>
-      </c>
-      <c r="AS17" s="50">
-        <f t="shared" si="36"/>
-        <v>2.2528766945869704E-15</v>
-      </c>
-      <c r="AT17" s="50">
-        <f t="shared" si="37"/>
-        <v>1.1264383472934852E-13</v>
-      </c>
-      <c r="AV17" s="1">
-        <f t="shared" si="38"/>
-        <v>2.3853601450756169E-11</v>
-      </c>
-      <c r="AW17" s="50">
-        <f t="shared" si="39"/>
-        <v>1.7040000000000001E-9</v>
-      </c>
-      <c r="AX17" s="50">
-        <f t="shared" si="40"/>
-        <v>1.9082881160604935E-10</v>
-      </c>
-      <c r="AY17" s="1">
-        <f t="shared" si="41"/>
-        <v>2.4796314728046389E-12</v>
-      </c>
-      <c r="BA17" s="1">
-        <f t="shared" si="42"/>
-        <v>2.3207851058447629E-11</v>
-      </c>
-      <c r="BB17" s="50">
-        <f t="shared" si="43"/>
-        <v>9.8400000000000012E-10</v>
-      </c>
-      <c r="BC17" s="50">
-        <f t="shared" si="44"/>
-        <v>1.8566280846758103E-10</v>
-      </c>
-      <c r="BD17" s="1">
-        <f t="shared" si="45"/>
-        <v>1.552133137270982E-12</v>
-      </c>
-      <c r="BH17" s="98"/>
-      <c r="BI17" s="98"/>
-      <c r="BJ17" s="98"/>
-      <c r="BK17" s="91"/>
-      <c r="BL17" s="91"/>
-      <c r="BM17" s="98"/>
-      <c r="BN17" s="98"/>
-      <c r="BO17" s="91"/>
-      <c r="BP17" s="91"/>
-      <c r="BQ17" s="91"/>
-      <c r="BR17" s="98"/>
-      <c r="BS17" s="98"/>
-      <c r="BT17" s="91"/>
-      <c r="BU17" s="91"/>
-    </row>
-    <row r="18" spans="1:73">
-      <c r="A18" s="77">
-        <v>3900</v>
-      </c>
-      <c r="B18" s="84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="77">
-        <v>13.8932319612138</v>
-      </c>
-      <c r="D18" s="77">
-        <v>1.5845935583510899</v>
-      </c>
-      <c r="E18" s="77">
-        <v>23.5846443194594</v>
-      </c>
-      <c r="F18" s="77">
-        <v>1.7056280294042601</v>
-      </c>
-      <c r="AR18" s="50">
-        <f t="shared" si="35"/>
         <v>1.8181748887077827E-11</v>
       </c>
       <c r="AS18" s="50">
@@ -7425,31 +7411,31 @@
         <v>9.9899719159768355E-14</v>
       </c>
       <c r="AV18" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>2.0421794413363857E-11</v>
       </c>
       <c r="AW18" s="50">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1.7040000000000001E-9</v>
       </c>
       <c r="AX18" s="50">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1.6337435530691085E-10</v>
       </c>
       <c r="AY18" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>3.2459260978402183E-12</v>
       </c>
       <c r="BA18" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1.9697537279304226E-11</v>
       </c>
       <c r="BB18" s="50">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>9.8400000000000012E-10</v>
       </c>
       <c r="BC18" s="50">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>1.5758029823443381E-10</v>
       </c>
       <c r="BD18" s="1">
@@ -7457,195 +7443,195 @@
         <v>1.4794459496423484E-12</v>
       </c>
     </row>
-    <row r="19" spans="1:73">
-      <c r="A19" s="77">
+    <row r="19" spans="1:71">
+      <c r="A19" s="67">
         <v>4000</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="77">
+      <c r="C19" s="67">
         <v>14.159840771141599</v>
       </c>
-      <c r="D19" s="77">
+      <c r="D19" s="67">
         <v>1.41688638932538</v>
       </c>
-      <c r="E19" s="77">
+      <c r="E19" s="67">
         <v>24.307674223869199</v>
       </c>
-      <c r="F19" s="77">
+      <c r="F19" s="67">
         <v>1.67317466996315</v>
       </c>
     </row>
-    <row r="20" spans="1:73">
-      <c r="A20" s="77">
+    <row r="20" spans="1:71">
+      <c r="A20" s="67">
         <v>4050</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="77">
+      <c r="C20" s="67">
         <v>14.202986215545801</v>
       </c>
-      <c r="D20" s="77">
+      <c r="D20" s="67">
         <v>1.5927004496706401</v>
       </c>
-      <c r="E20" s="77">
+      <c r="E20" s="67">
         <v>24.109663560267101</v>
       </c>
-      <c r="F20" s="77">
+      <c r="F20" s="67">
         <v>1.7477286396192699</v>
       </c>
     </row>
-    <row r="21" spans="1:73">
-      <c r="A21" s="77">
+    <row r="21" spans="1:71">
+      <c r="A21" s="67">
         <v>4100</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="77">
+      <c r="C21" s="67">
         <v>14.1477581631242</v>
       </c>
-      <c r="D21" s="77">
+      <c r="D21" s="67">
         <v>0.96726917441917404</v>
       </c>
-      <c r="E21" s="77">
+      <c r="E21" s="67">
         <v>23.991469043145798</v>
       </c>
-      <c r="F21" s="77">
+      <c r="F21" s="67">
         <v>1.0661672525943</v>
       </c>
     </row>
-    <row r="22" spans="1:73">
-      <c r="A22" s="77">
+    <row r="22" spans="1:71">
+      <c r="A22" s="67">
         <v>4200</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="77">
+      <c r="C22" s="67">
         <v>13.998592400678501</v>
       </c>
-      <c r="D22" s="77">
+      <c r="D22" s="67">
         <v>1.4551827892046001</v>
       </c>
-      <c r="E22" s="77">
+      <c r="E22" s="67">
         <v>23.585214490292302</v>
       </c>
-      <c r="F22" s="77">
+      <c r="F22" s="67">
         <v>1.5773710744623799</v>
       </c>
     </row>
-    <row r="23" spans="1:73">
-      <c r="A23" s="77">
+    <row r="23" spans="1:71">
+      <c r="A23" s="67">
         <v>4350</v>
       </c>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="77">
+      <c r="C23" s="67">
         <v>12.7285216590373</v>
       </c>
-      <c r="D23" s="77">
+      <c r="D23" s="67">
         <v>1.5238300246508001</v>
       </c>
-      <c r="E23" s="77">
+      <c r="E23" s="67">
         <v>21.3442985608926</v>
       </c>
-      <c r="F23" s="77">
+      <c r="F23" s="67">
         <v>1.6759499431585601</v>
       </c>
     </row>
-    <row r="24" spans="1:73">
-      <c r="A24" s="77">
+    <row r="24" spans="1:71">
+      <c r="A24" s="67">
         <v>4350</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="77">
+      <c r="C24" s="67">
         <v>14.295788703025901</v>
       </c>
-      <c r="D24" s="77">
+      <c r="D24" s="67">
         <v>0.95743396407127301</v>
       </c>
-      <c r="E24" s="77">
+      <c r="E24" s="67">
         <v>24.0058440474461</v>
       </c>
-      <c r="F24" s="77">
+      <c r="F24" s="67">
         <v>1.0609821789779801</v>
       </c>
     </row>
-    <row r="25" spans="1:73">
-      <c r="A25" s="77">
+    <row r="25" spans="1:71">
+      <c r="A25" s="67">
         <v>4500</v>
       </c>
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="77">
+      <c r="C25" s="67">
         <v>12.652912148520899</v>
       </c>
-      <c r="D25" s="77">
+      <c r="D25" s="67">
         <v>1.2770471819939999</v>
       </c>
-      <c r="E25" s="77">
+      <c r="E25" s="67">
         <v>21.557679219558601</v>
       </c>
-      <c r="F25" s="77">
+      <c r="F25" s="67">
         <v>1.4151791181836999</v>
       </c>
     </row>
-    <row r="26" spans="1:73">
-      <c r="A26" s="77">
+    <row r="26" spans="1:71">
+      <c r="A26" s="67">
         <v>4500</v>
       </c>
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="77">
+      <c r="C26" s="67">
         <v>13.8576230407855</v>
       </c>
-      <c r="D26" s="77">
+      <c r="D26" s="67">
         <v>0.96053842000012601</v>
       </c>
-      <c r="E26" s="77">
+      <c r="E26" s="67">
         <v>22.9614197110436</v>
       </c>
-      <c r="F26" s="77">
+      <c r="F26" s="67">
         <v>1.05034657780143</v>
       </c>
     </row>
-    <row r="27" spans="1:73">
-      <c r="A27" s="77">
+    <row r="27" spans="1:71">
+      <c r="A27" s="67">
         <v>4550</v>
       </c>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="77">
+      <c r="C27" s="67">
         <v>11.9846211346032</v>
       </c>
-      <c r="D27" s="77">
+      <c r="D27" s="67">
         <v>1.90488620765271</v>
       </c>
-      <c r="E27" s="77">
+      <c r="E27" s="67">
         <v>20.0178224383173</v>
       </c>
-      <c r="F27" s="77">
+      <c r="F27" s="67">
         <v>1.5035019813438499</v>
       </c>
     </row>
-    <row r="28" spans="1:73">
-      <c r="A28" s="79" t="s">
+    <row r="28" spans="1:71">
+      <c r="A28" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="9">
